--- a/docs/dossiers/dossier-paris-20eme-arrondissement-76b6b82d.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-76b6b82d.xlsx
@@ -937,7 +937,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +347 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +326 €/mois.</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="B20" s="18" t="n">
-        <v>875.7</v>
+        <v>851.38</v>
       </c>
       <c r="C20" s="19" t="inlineStr">
         <is>
